--- a/downloads/inventory/dixani-stock-movement-register.xlsx
+++ b/downloads/inventory/dixani-stock-movement-register.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Movement Register" sheetId="1" r:id="R1487a4821ef24ce6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="R22fe51b544ab4b54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="3" r:id="R0e923e4c11b644c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Movement Register" sheetId="1" r:id="Rbd7224e5e0364a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="R3b5663e6c6844e66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="3" r:id="R902d9f3157aa43c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,7 +255,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -266,7 +266,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -277,7 +277,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -580,7 +580,7 @@
         <x:v>Currency</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>QAR</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="K5" t="str"/>
       <x:c r="L5" t="str"/>
@@ -1907,7 +1907,7 @@
       <x:formula1>"PCS,EA,BOX,CTN,KG,G,L,ML,M,SET,PACK"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="J5">
-      <x:formula1>"QAR,USD,EUR,GBP,AED,SAR,LKR,INR"</x:formula1>
+      <x:formula1>"USD,EUR,GBP,CAD,AUD,NZD,CHF,JPY,CNY,HKD,SGD,INR,AED,SAR,QAR,LKR,ZAR,BRL,MXN"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
